--- a/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
+++ b/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
@@ -3782,6 +3782,11 @@
           <t>+9.09</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>130565</t>
@@ -5932,6 +5937,11 @@
           <t>42844</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7992,6 +8002,11 @@
           <t>+0.99</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>130565</t>
@@ -9477,6 +9492,11 @@
           <t>42844</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11862,6 +11882,11 @@
           <t>+11.41</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>104583</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16227,6 +16252,11 @@
           <t>+4.51</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>142573</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -18862,6 +18892,11 @@
           <t>+9.61</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>104583</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -21632,6 +21667,11 @@
           <t>+12.98</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>142573</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -23627,6 +23667,11 @@
           <t>45.94</t>
         </is>
       </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -30065,6 +30110,11 @@
           <t>+3.30</t>
         </is>
       </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S405" t="inlineStr">
         <is>
           <t>130565</t>
@@ -35056,6 +35106,11 @@
           <t>+8.96</t>
         </is>
       </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S473" t="inlineStr">
         <is>
           <t>130565</t>
@@ -42086,6 +42141,11 @@
           <t>45.31</t>
         </is>
       </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -46837,6 +46897,11 @@
       <c r="Q638" t="inlineStr">
         <is>
           <t>+0.24</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>95617</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52215,6 +52280,94 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Yarisleidis</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CIRILO DUBOYS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Frederikke Hauge</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>MATTHIESEN</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>104583</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Saman</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SOLTANI</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>142573</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Fernando Dayan</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>JORGE ENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
+++ b/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
@@ -2212,6 +2212,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>118986</t>
@@ -6382,6 +6387,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9272,6 +9282,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -24832,6 +24847,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T337" t="inlineStr">
         <is>
           <t>118986</t>
@@ -29194,6 +29214,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T394" t="inlineStr">
         <is>
           <t>118986</t>
@@ -30935,6 +30960,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -36243,6 +36273,11 @@
       <c r="R488" t="inlineStr">
         <is>
           <t>64580</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>61249</t>
         </is>
       </c>
     </row>
@@ -47276,7 +47311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52368,6 +52403,28 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Aly</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
+++ b/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
@@ -47344,7 +47344,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>del RIO Adrian</t>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>del RIO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -47361,7 +47366,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>van der WESTHUYZEN Jean</t>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>van der WESTHUYZEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -47378,7 +47388,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>van der WESTHUYZEN Pierre</t>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>van der WESTHUYZEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
+++ b/events/Paris_2024_OG/Paris_2024_OG_Results.xlsx
@@ -2307,6 +2307,11 @@
           <t>113848</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>98683</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5872,6 +5877,11 @@
           <t>71243</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>142552</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15382,6 +15392,11 @@
           <t>+8.02</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>52750</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15927,6 +15942,11 @@
           <t>+3.77</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -19602,6 +19622,11 @@
           <t>+4.12</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>52750</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -20852,6 +20877,11 @@
           <t>+1.53</t>
         </is>
       </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -25112,6 +25142,11 @@
           <t>113848</t>
         </is>
       </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>98683</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -31855,6 +31890,11 @@
           <t>71243</t>
         </is>
       </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>142552</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -33455,6 +33495,11 @@
           <t>+1.59</t>
         </is>
       </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -35603,6 +35648,11 @@
           <t>71243</t>
         </is>
       </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>142552</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -37701,6 +37751,11 @@
       <c r="Q507" t="inlineStr">
         <is>
           <t>+1.10</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>79493</t>
         </is>
       </c>
     </row>
@@ -47311,7 +47366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52440,6 +52495,94 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>52750</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>AGHAMIRZAEIJENAGHRAD</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Jose Ramon</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>PELIER CORDOVA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>98683</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Toshka</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>BESHARAH</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>142552</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Yule</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>CHEN</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
